--- a/data/trans_orig/IP16A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Provincia-trans_orig.xlsx
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31370</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>143939</t>
+          <t>143453</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>301250</t>
+          <t>302149</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>58666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106835</t>
+          <t>106433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71217</t>
+          <t>71291</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>171033</t>
+          <t>171965</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>177170</t>
+          <t>177218</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>354179</t>
+          <t>354228</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>359340</t>
+          <t>359361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Provincia-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11668</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16730</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16351</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,47 +2208,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2551,47 +2551,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2894,47 +2894,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>21499</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3007,57 +3007,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3237,47 +3237,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>25924</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3350,57 +3350,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3580,47 +3580,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3693,57 +3693,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3867,7 +3867,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3878,7 +3878,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4159,47 +4159,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18024</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15612</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4272,57 +4272,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18024</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18024</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18024</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15612</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15612</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15612</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4502,47 +4502,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>23483</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4615,57 +4615,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>23483</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>23483</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>23483</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4845,47 +4845,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22309</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15530</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22309</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22309</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22309</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22309</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15530</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15530</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15530</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>22309</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>22309</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>22309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5075,107 +5075,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3173</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3463</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -5188,74 +5188,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15242</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18663</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16146</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16595</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>19319</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>85,9%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>15242</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>48</t>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5301,57 +5301,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15242</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15242</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>15242</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>19319</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>19319</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>19319</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>15242</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>15242</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>15242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5531,47 +5531,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12287</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>14507</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>12287</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5644,57 +5644,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12287</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12287</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12287</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14507</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>14507</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>14507</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12287</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>12287</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>12287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5874,47 +5874,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10988</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>18093</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5987,57 +5987,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>10988</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>10988</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>10988</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>18093</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>18093</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>18093</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6217,47 +6217,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25345</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>26559</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>25345</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6330,57 +6330,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25345</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>25345</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>25345</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>26559</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>26559</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>26559</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>25345</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>25345</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>25345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6560,47 +6560,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>21692</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>21223</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>21692</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6673,57 +6673,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>21692</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>21692</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>21692</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>21223</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>21223</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>21223</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>21692</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>21692</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>21692</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6790,107 +6790,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3768</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -6903,74 +6903,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>146565</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>143453</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>143966</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>433</t>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>302149</t>
+          <t>301725</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7016,57 +7016,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7201,7 +7201,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7482,47 +7482,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16092</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7595,57 +7595,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>16092</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>16092</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>16092</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7825,47 +7825,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20682</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>27263</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20682</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7938,57 +7938,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20682</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20682</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20682</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>27263</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>27263</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>27263</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20682</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20682</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8168,47 +8168,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>9523</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8339</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8281,57 +8281,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9523</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>9523</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>9523</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8339</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8339</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8511,47 +8511,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25580</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>23799</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25580</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8624,57 +8624,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25580</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25580</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>25580</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>23799</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>23799</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>23799</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>25580</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>25580</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>25580</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8854,47 +8854,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>6511</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5168</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8967,57 +8967,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6511</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>6511</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>6511</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5168</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5168</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9197,47 +9197,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>9105</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>8685</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9310,57 +9310,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>9105</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>9105</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>9105</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>8685</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>8685</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>8685</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9540,47 +9540,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>14250</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9653,57 +9653,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>14250</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>14250</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>14250</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9883,47 +9883,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>25012</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>20919</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>25012</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9996,57 +9996,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>25012</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>25012</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>25012</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>20919</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>20919</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>20919</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>25012</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>25012</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>25012</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10226,47 +10226,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -10339,57 +10339,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -10524,7 +10524,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -10805,64 +10805,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>20800</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22322</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -10918,57 +10918,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11035,107 +11035,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4388</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4458</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4784</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -11148,74 +11148,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>62235</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58666</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63054</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>37900</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>34309</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38767</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>48163</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>125</t>
@@ -11223,27 +11223,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>110398</t>
+          <t>80568</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106433</t>
+          <t>77104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111217</t>
+          <t>81435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11261,57 +11261,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>63054</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>63054</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>63054</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>111217</t>
+          <t>81435</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111217</t>
+          <t>81435</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111217</t>
+          <t>81435</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11491,64 +11491,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>17199</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20287</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -11604,57 +11604,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11834,64 +11834,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12223</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11073</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -11947,57 +11947,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12177,64 +12177,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8440</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>10689</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -12290,57 +12290,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12520,64 +12520,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7662</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>13607</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -12633,57 +12633,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12750,107 +12750,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3482</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -12863,74 +12863,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>29200</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>26407</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>88,66%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>29727</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>27829</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>30268</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>91,94%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>44354</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>96</t>
@@ -12938,27 +12938,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>73554</t>
+          <t>71759</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71291</t>
+          <t>68818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -12976,57 +12976,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13093,107 +13093,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3247</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>40,03%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>38,49%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -13206,74 +13206,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>4866</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>91,21%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>6981</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>4701</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7634</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>91,44%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>61,58%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>11707</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -13281,27 +13281,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13319,57 +13319,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13436,72 +13436,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -13549,72 +13549,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>175597</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>171965</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>177218</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>140931</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136871</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142464</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>357798</t>
+          <t>305883</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>354228</t>
+          <t>301474</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>359361</t>
+          <t>307395</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -13662,57 +13662,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
